--- a/_pythonscripts/all-members.xlsx
+++ b/_pythonscripts/all-members.xlsx
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
